--- a/output/IS/expanded_mapping_cosine_SkillNER RAKE_KeyBERT_IS.xlsx
+++ b/output/IS/expanded_mapping_cosine_SkillNER RAKE_KeyBERT_IS.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Problem management 2</t>
+          <t>Problem management 5</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Problem management 3</t>
+          <t>Problem management 2</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -483,7 +483,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Problem management 5</t>
+          <t>Problem management 4</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -498,7 +498,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Problem management 4</t>
+          <t>Problem management 3</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -543,7 +543,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Measurement 3</t>
+          <t>Measurement 4</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -558,7 +558,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Measurement 4</t>
+          <t>Measurement 6</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -573,7 +573,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Measurement 6</t>
+          <t>Measurement 5</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -588,7 +588,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Measurement 5</t>
+          <t>Measurement 2</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -603,7 +603,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Measurement 2</t>
+          <t>Measurement 3</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -648,7 +648,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Infrastructure operations 1</t>
+          <t>Infrastructure operations 4</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -678,7 +678,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Infrastructure operations 3</t>
+          <t>Infrastructure operations 1</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -693,7 +693,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Infrastructure operations 4</t>
+          <t>Infrastructure operations 3</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -708,7 +708,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Infrastructure operations 1</t>
+          <t>Infrastructure operations 2</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -723,7 +723,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Infrastructure operations 2</t>
+          <t>Infrastructure operations 1</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -798,7 +798,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vulnerability assessment 4</t>
+          <t>Vulnerability assessment 3</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -813,7 +813,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vulnerability assessment 3</t>
+          <t>Vulnerability assessment 4</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -858,7 +858,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sustainability 5</t>
+          <t>Sustainability 6</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -873,7 +873,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sustainability 6</t>
+          <t>Sustainability 5</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -918,7 +918,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>User acceptance testing 6</t>
+          <t>User acceptance testing 3</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -948,7 +948,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>User acceptance testing 3</t>
+          <t>User acceptance testing 6</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -978,7 +978,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Incident management 3</t>
+          <t>Incident management 1</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Incident management 4</t>
+          <t>Incident management 3</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Incident management 1</t>
+          <t>Incident management 4</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>User acceptance testing 2</t>
+          <t>User acceptance testing 5</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>User acceptance testing 5</t>
+          <t>User acceptance testing 2</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sales support 4</t>
+          <t>Sales support 6</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sales support 2</t>
+          <t>Sales support 4</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sales support 3</t>
+          <t>Sales support 2</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sales support 6</t>
+          <t>Sales support 5</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sales support 5</t>
+          <t>Sales support 3</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sales support 2</t>
+          <t>Sales support 1</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sales support 1</t>
+          <t>Sales support 2</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Customer service support 2</t>
+          <t>Customer service support 1</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Customer service support 1</t>
+          <t>Customer service support 2</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Data analytics 4</t>
+          <t>Data analytics 2</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Data analytics 3</t>
+          <t>Data analytics 4</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Data analytics 2</t>
+          <t>Data analytics 6</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Data analytics 6</t>
+          <t>Data analytics 3</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Budgeting and forecasting 2</t>
+          <t>Budgeting and forecasting 3</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Budgeting and forecasting 3</t>
+          <t>Budgeting and forecasting 2</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Information management 6</t>
+          <t>Information management 4</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Information management 4</t>
+          <t>Information management 5</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Information management 5</t>
+          <t>Information management 6</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Business situation analysis 3</t>
+          <t>Business situation analysis 4</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Business situation analysis 4</t>
+          <t>Business situation analysis 3</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Business intelligence 4</t>
+          <t>Business intelligence 3</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Business intelligence 3</t>
+          <t>Business intelligence 4</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Business intelligence 4</t>
+          <t>Business intelligence 3</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Business intelligence 3</t>
+          <t>Business intelligence 4</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Threat intelligence 3</t>
+          <t>Threat intelligence 2</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Threat intelligence 2</t>
+          <t>Threat intelligence 5</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Threat intelligence 4</t>
+          <t>Threat intelligence 3</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Threat intelligence 5</t>
+          <t>Threat intelligence 4</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Business process improvement 2</t>
+          <t>Business process improvement 3</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Business process improvement 3</t>
+          <t>Business process improvement 2</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Threat intelligence 3</t>
+          <t>Threat intelligence 2</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Threat intelligence 2</t>
+          <t>Threat intelligence 3</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Business process improvement 2</t>
+          <t>Business process improvement 3</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Business process improvement 3</t>
+          <t>Business process improvement 2</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Business process improvement 5</t>
+          <t>Business process improvement 2</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Business process improvement 3</t>
+          <t>Business process improvement 5</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Business process improvement 2</t>
+          <t>Business process improvement 6</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Business process improvement 4</t>
+          <t>Business process improvement 3</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Business process improvement 6</t>
+          <t>Business process improvement 4</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Threat intelligence 4</t>
+          <t>Threat intelligence 2</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Threat intelligence 2</t>
+          <t>Threat intelligence 4</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Business process improvement 5</t>
+          <t>Business process improvement 3</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Business process improvement 3</t>
+          <t>Business process improvement 5</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Contract management 6</t>
+          <t>Contract management 5</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Contract management 5</t>
+          <t>Contract management 2</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Contract management 2</t>
+          <t>Contract management 6</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Contract management 3</t>
+          <t>Contract management 4</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Contract management 2</t>
+          <t>Contract management 3</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Contract management 4</t>
+          <t>Contract management 2</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>User acceptance testing 2</t>
+          <t>User acceptance testing 3</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>User acceptance testing 3</t>
+          <t>User acceptance testing 2</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Business situation analysis 3</t>
+          <t>Business situation analysis 4</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Business situation analysis 4</t>
+          <t>Business situation analysis 3</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Business process improvement 2</t>
+          <t>Business process improvement 3</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Business process improvement 3</t>
+          <t>Business process improvement 2</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Business process improvement 2</t>
+          <t>Business process improvement 3</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Business process improvement 3</t>
+          <t>Business process improvement 2</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Business process improvement 5</t>
+          <t>Business process improvement 2</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Business process improvement 3</t>
+          <t>Business process improvement 5</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Business process improvement 2</t>
+          <t>Business process improvement 6</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Business process improvement 4</t>
+          <t>Business process improvement 3</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Business process improvement 6</t>
+          <t>Business process improvement 4</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Business process improvement 5</t>
+          <t>Business process improvement 2</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Business process improvement 3</t>
+          <t>Business process improvement 5</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Business process improvement 2</t>
+          <t>Business process improvement 6</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Business process improvement 4</t>
+          <t>Business process improvement 3</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Business process improvement 6</t>
+          <t>Business process improvement 4</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Business process improvement 5</t>
+          <t>Business process improvement 3</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Business process improvement 3</t>
+          <t>Business process improvement 5</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Quality management 2</t>
+          <t>Quality management 3</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Quality management 3</t>
+          <t>Quality management 2</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Sales support 4</t>
+          <t>Sales support 6</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Sales support 2</t>
+          <t>Sales support 4</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Sales support 3</t>
+          <t>Sales support 2</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Sales support 6</t>
+          <t>Sales support 5</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Sales support 5</t>
+          <t>Sales support 3</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>High-performance computing 7</t>
+          <t>High-performance computing 5</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>High-performance computing 5</t>
+          <t>High-performance computing 7</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Real-time/embedded systems development 4</t>
+          <t>Real-time/embedded systems development 6</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Real-time/embedded systems development 5</t>
+          <t>Real-time/embedded systems development 4</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Real-time/embedded systems development 6</t>
+          <t>Real-time/embedded systems development 5</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Real-time/embedded systems development 4</t>
+          <t>Real-time/embedded systems development 3</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Real-time/embedded systems development 3</t>
+          <t>Real-time/embedded systems development 4</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Systems and software lifecycle engineering 4</t>
+          <t>Systems and software lifecycle engineering 3</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Systems and software lifecycle engineering 3</t>
+          <t>Systems and software lifecycle engineering 5</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Systems and software lifecycle engineering 5</t>
+          <t>Systems and software lifecycle engineering 4</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3198,7 +3198,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Data analytics 4</t>
+          <t>Data analytics 2</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Data analytics 3</t>
+          <t>Data analytics 4</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Data analytics 2</t>
+          <t>Data analytics 6</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Data analytics 6</t>
+          <t>Data analytics 3</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Data analytics 3</t>
+          <t>Data analytics 2</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Data analytics 2</t>
+          <t>Data analytics 3</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Sales support 4</t>
+          <t>Sales support 6</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Sales support 2</t>
+          <t>Sales support 4</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Sales support 3</t>
+          <t>Sales support 2</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Sales support 6</t>
+          <t>Sales support 5</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3393,7 +3393,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Sales support 5</t>
+          <t>Sales support 3</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Sales support 2</t>
+          <t>Sales support 1</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Sales support 1</t>
+          <t>Sales support 2</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Sales support 2</t>
+          <t>Sales support 1</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Sales support 1</t>
+          <t>Sales support 2</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Sales support 3</t>
+          <t>Sales support 5</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Sales support 5</t>
+          <t>Sales support 3</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Strategic planning 4</t>
+          <t>Strategic planning 5</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Strategic planning 7</t>
+          <t>Strategic planning 4</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Strategic planning 5</t>
+          <t>Strategic planning 7</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Strategic planning 4</t>
+          <t>Strategic planning 5</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Strategic planning 5</t>
+          <t>Strategic planning 4</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Data science 2</t>
+          <t>Data science 4</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Data science 4</t>
+          <t>Data science 2</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Security operations 1</t>
+          <t>Security operations 4</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Security operations 4</t>
+          <t>Security operations 2</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Security operations 2</t>
+          <t>Security operations 1</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Sales support 3</t>
+          <t>Sales support 1</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Sales support 4</t>
+          <t>Sales support 3</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Sales support 1</t>
+          <t>Sales support 4</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Financial analysis 2</t>
+          <t>Financial analysis 5</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Financial analysis 6</t>
+          <t>Financial analysis 4</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Financial analysis 5</t>
+          <t>Financial analysis 2</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Financial analysis 4</t>
+          <t>Financial analysis 6</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Data science 5</t>
+          <t>Data science 4</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Data science 4</t>
+          <t>Data science 5</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Sales support 3</t>
+          <t>Sales support 1</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Sales support 2</t>
+          <t>Sales support 3</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Sales support 1</t>
+          <t>Sales support 2</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Application support 4</t>
+          <t>Application support 2</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Application support 2</t>
+          <t>Application support 4</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Analytical classification and coding 3</t>
+          <t>Analytical classification and coding 2</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Analytical classification and coding 2</t>
+          <t>Analytical classification and coding 3</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Data management 3</t>
+          <t>Data management 4</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Data management 2</t>
+          <t>Data management 3</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Data management 4</t>
+          <t>Data management 5</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Data management 5</t>
+          <t>Data management 2</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Knowledge management 4</t>
+          <t>Knowledge management 3</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Knowledge management 3</t>
+          <t>Knowledge management 4</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Infrastructure operations 1</t>
+          <t>Infrastructure operations 2</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Infrastructure operations 2</t>
+          <t>Infrastructure operations 1</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Portfolio, programme and project support 5</t>
+          <t>Portfolio, programme and project support 2</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Portfolio, programme and project support 2</t>
+          <t>Portfolio, programme and project support 4</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Portfolio, programme and project support 4</t>
+          <t>Portfolio, programme and project support 5</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Functional testing 4</t>
+          <t>Functional testing 3</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Functional testing 3</t>
+          <t>Functional testing 1</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Functional testing 2</t>
+          <t>Functional testing 4</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Functional testing 5</t>
+          <t>Functional testing 2</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Functional testing 1</t>
+          <t>Functional testing 5</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Infrastructure operations 1</t>
+          <t>Infrastructure operations 2</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Infrastructure operations 2</t>
+          <t>Infrastructure operations 1</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Database design 4</t>
+          <t>Database design 3</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Database design 2</t>
+          <t>Database design 4</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Database design 5</t>
+          <t>Database design 2</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Database design 3</t>
+          <t>Database design 5</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Database administration 4</t>
+          <t>Database administration 3</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Database administration 3</t>
+          <t>Database administration 4</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Database design 4</t>
+          <t>Database design 3</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Database design 2</t>
+          <t>Database design 4</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Database design 3</t>
+          <t>Database design 2</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Graphic design 2</t>
+          <t>Graphic design 3</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Graphic design 3</t>
+          <t>Graphic design 1</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Graphic design 1</t>
+          <t>Graphic design 2</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Graphic design 2</t>
+          <t>Graphic design 1</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Graphic design 1</t>
+          <t>Graphic design 2</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Configuration management 5</t>
+          <t>Configuration management 3</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Configuration management 4</t>
+          <t>Configuration management 2</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -4908,7 +4908,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Configuration management 2</t>
+          <t>Configuration management 5</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Configuration management 3</t>
+          <t>Configuration management 4</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Configuration management 4</t>
+          <t>Configuration management 3</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Configuration management 3</t>
+          <t>Configuration management 4</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Measurement 3</t>
+          <t>Measurement 4</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Measurement 4</t>
+          <t>Measurement 6</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Measurement 6</t>
+          <t>Measurement 5</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Measurement 5</t>
+          <t>Measurement 2</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Measurement 2</t>
+          <t>Measurement 3</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Database administration 4</t>
+          <t>Database administration 3</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Database administration 3</t>
+          <t>Database administration 4</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Configuration management 2</t>
+          <t>Configuration management 5</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Configuration management 3</t>
+          <t>Configuration management 6</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Configuration management 5</t>
+          <t>Configuration management 2</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Configuration management 6</t>
+          <t>Configuration management 4</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Configuration management 4</t>
+          <t>Configuration management 3</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Deployment 6</t>
+          <t>Deployment 5</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Deployment 5</t>
+          <t>Deployment 3</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Deployment 3</t>
+          <t>Deployment 6</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Brand management 6</t>
+          <t>Brand management 4</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Brand management 4</t>
+          <t>Brand management 5</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Brand management 5</t>
+          <t>Brand management 6</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Network support 5</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Network support 3</t>
+          <t>Network support 5</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 3</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Business situation analysis 5</t>
+          <t>Business situation analysis 2</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Business situation analysis 2</t>
+          <t>Business situation analysis 5</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Business situation analysis 3</t>
+          <t>Business situation analysis 4</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Business situation analysis 4</t>
+          <t>Business situation analysis 3</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Systems integration and build 4</t>
+          <t>Systems integration and build 2</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Systems integration and build 3</t>
+          <t>Systems integration and build 4</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Systems integration and build 2</t>
+          <t>Systems integration and build 3</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Configuration management 2</t>
+          <t>Configuration management 3</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Configuration management 3</t>
+          <t>Configuration management 2</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -5613,7 +5613,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Graphic design 2</t>
+          <t>Graphic design 1</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Graphic design 1</t>
+          <t>Graphic design 2</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Quality assurance 6</t>
+          <t>Quality assurance 5</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Quality assurance 5</t>
+          <t>Quality assurance 3</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Quality assurance 4</t>
+          <t>Quality assurance 2</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Quality assurance 3</t>
+          <t>Quality assurance 4</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Quality assurance 2</t>
+          <t>Quality assurance 6</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Analytical classification and coding 3</t>
+          <t>Analytical classification and coding 4</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Analytical classification and coding 4</t>
+          <t>Analytical classification and coding 3</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Brand management 6</t>
+          <t>Brand management 4</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Brand management 4</t>
+          <t>Brand management 5</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Brand management 5</t>
+          <t>Brand management 6</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -5988,7 +5988,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Application support 4</t>
+          <t>Application support 2</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Application support 2</t>
+          <t>Application support 4</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Application support 4</t>
+          <t>Application support 2</t>
         </is>
       </c>
       <c r="C375" t="n">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Application support 2</t>
+          <t>Application support 4</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 2</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Penetration testing 2</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 4</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Penetration testing 4</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Information management 6</t>
+          <t>Information management 4</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Information management 4</t>
+          <t>Information management 5</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Information management 5</t>
+          <t>Information management 6</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Penetration testing 5</t>
+          <t>Penetration testing 2</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Penetration testing 2</t>
+          <t>Penetration testing 4</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Penetration testing 4</t>
+          <t>Penetration testing 5</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Penetration testing 5</t>
+          <t>Penetration testing 4</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 2</t>
         </is>
       </c>
       <c r="C395" t="n">
@@ -6363,7 +6363,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Penetration testing 2</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Penetration testing 4</t>
+          <t>Penetration testing 5</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Deployment 6</t>
+          <t>Deployment 5</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -6408,7 +6408,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Deployment 5</t>
+          <t>Deployment 3</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Deployment 3</t>
+          <t>Deployment 6</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Deployment 5</t>
+          <t>Deployment 3</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Deployment 3</t>
+          <t>Deployment 2</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Deployment 2</t>
+          <t>Deployment 4</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Deployment 4</t>
+          <t>Deployment 5</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Information management 6</t>
+          <t>Information management 4</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Information management 4</t>
+          <t>Information management 5</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -6633,7 +6633,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Information management 5</t>
+          <t>Information management 6</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Information management 7</t>
+          <t>Information management 3</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Information management 6</t>
+          <t>Information management 5</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Information management 3</t>
+          <t>Information management 6</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Information management 5</t>
+          <t>Information management 7</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Audit 6</t>
+          <t>Audit 3</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -6753,7 +6753,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Audit 3</t>
+          <t>Audit 6</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -6858,7 +6858,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Risk management 4</t>
+          <t>Risk management 7</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Risk management 2</t>
+          <t>Risk management 5</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Risk management 7</t>
+          <t>Risk management 2</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Risk management 5</t>
+          <t>Risk management 4</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Audit 6</t>
+          <t>Audit 3</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Audit 3</t>
+          <t>Audit 6</t>
         </is>
       </c>
       <c r="C437" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Risk management 3</t>
+          <t>Risk management 4</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Risk management 4</t>
+          <t>Risk management 3</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Project management 4</t>
+          <t>Project management 7</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Project management 5</t>
+          <t>Project management 4</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Project management 7</t>
+          <t>Project management 5</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Project management 4</t>
+          <t>Project management 7</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Project management 5</t>
+          <t>Project management 4</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Project management 7</t>
+          <t>Project management 5</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Risk management 4</t>
+          <t>Risk management 7</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Risk management 2</t>
+          <t>Risk management 5</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -7338,7 +7338,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Risk management 7</t>
+          <t>Risk management 2</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Risk management 5</t>
+          <t>Risk management 4</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Risk management 3</t>
+          <t>Risk management 4</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Risk management 4</t>
+          <t>Risk management 3</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Risk management 4</t>
+          <t>Risk management 6</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Risk management 6</t>
+          <t>Risk management 5</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Risk management 5</t>
+          <t>Risk management 4</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Knowledge management 4</t>
+          <t>Knowledge management 3</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Knowledge management 3</t>
+          <t>Knowledge management 4</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Risk management 3</t>
+          <t>Risk management 4</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -7668,7 +7668,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Risk management 4</t>
+          <t>Risk management 3</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -7683,7 +7683,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>Risk management 2</t>
+          <t>Risk management 5</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Risk management 5</t>
+          <t>Risk management 2</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Risk management 4</t>
+          <t>Risk management 7</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Risk management 2</t>
+          <t>Risk management 5</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Risk management 7</t>
+          <t>Risk management 2</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -7833,7 +7833,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Risk management 5</t>
+          <t>Risk management 4</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Risk management 3</t>
+          <t>Risk management 4</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Risk management 4</t>
+          <t>Risk management 3</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Project management 4</t>
+          <t>Project management 7</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Project management 5</t>
+          <t>Project management 4</t>
         </is>
       </c>
       <c r="C505" t="n">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Project management 7</t>
+          <t>Project management 5</t>
         </is>
       </c>
       <c r="C506" t="n">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Audit 6</t>
+          <t>Audit 3</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Audit 3</t>
+          <t>Audit 6</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Risk management 4</t>
+          <t>Risk management 6</t>
         </is>
       </c>
       <c r="C516" t="n">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Risk management 6</t>
+          <t>Risk management 5</t>
         </is>
       </c>
       <c r="C517" t="n">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Risk management 5</t>
+          <t>Risk management 4</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Software design 3</t>
+          <t>Software design 4</t>
         </is>
       </c>
       <c r="C521" t="n">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Software design 6</t>
+          <t>Software design 2</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Software design 2</t>
+          <t>Software design 6</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -8298,7 +8298,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Software design 4</t>
+          <t>Software design 3</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Information security 5</t>
+          <t>Information security 3</t>
         </is>
       </c>
       <c r="C526" t="n">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Information security 2</t>
+          <t>Information security 4</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Information security 4</t>
+          <t>Information security 2</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Information security 3</t>
+          <t>Information security 5</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Information management 6</t>
+          <t>Information management 4</t>
         </is>
       </c>
       <c r="C532" t="n">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Information management 4</t>
+          <t>Information management 5</t>
         </is>
       </c>
       <c r="C533" t="n">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Information management 5</t>
+          <t>Information management 6</t>
         </is>
       </c>
       <c r="C534" t="n">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Programme management 6</t>
+          <t>Programme management 7</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Programme management 7</t>
+          <t>Programme management 6</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Risk management 3</t>
+          <t>Risk management 4</t>
         </is>
       </c>
       <c r="C537" t="n">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Risk management 4</t>
+          <t>Risk management 3</t>
         </is>
       </c>
       <c r="C538" t="n">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Risk management 2</t>
+          <t>Risk management 5</t>
         </is>
       </c>
       <c r="C539" t="n">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Risk management 5</t>
+          <t>Risk management 2</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Information management 7</t>
+          <t>Information management 3</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Information management 6</t>
+          <t>Information management 5</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Information management 3</t>
+          <t>Information management 6</t>
         </is>
       </c>
       <c r="C547" t="n">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Information management 5</t>
+          <t>Information management 7</t>
         </is>
       </c>
       <c r="C548" t="n">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Network support 5</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C553" t="n">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Network support 3</t>
+          <t>Network support 5</t>
         </is>
       </c>
       <c r="C554" t="n">
@@ -8748,7 +8748,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 3</t>
         </is>
       </c>
       <c r="C555" t="n">
@@ -8793,7 +8793,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Hardware design 3</t>
+          <t>Hardware design 4</t>
         </is>
       </c>
       <c r="C558" t="n">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Hardware design 6</t>
+          <t>Hardware design 2</t>
         </is>
       </c>
       <c r="C559" t="n">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Hardware design 4</t>
+          <t>Hardware design 5</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Hardware design 2</t>
+          <t>Hardware design 3</t>
         </is>
       </c>
       <c r="C561" t="n">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Hardware design 5</t>
+          <t>Hardware design 6</t>
         </is>
       </c>
       <c r="C562" t="n">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C563" t="n">
@@ -8883,7 +8883,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C564" t="n">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C565" t="n">
@@ -8928,7 +8928,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C567" t="n">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Quality assurance 6</t>
+          <t>Quality assurance 5</t>
         </is>
       </c>
       <c r="C569" t="n">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Quality assurance 5</t>
+          <t>Quality assurance 3</t>
         </is>
       </c>
       <c r="C570" t="n">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Quality assurance 4</t>
+          <t>Quality assurance 2</t>
         </is>
       </c>
       <c r="C571" t="n">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Quality assurance 3</t>
+          <t>Quality assurance 4</t>
         </is>
       </c>
       <c r="C572" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Quality assurance 2</t>
+          <t>Quality assurance 6</t>
         </is>
       </c>
       <c r="C573" t="n">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Infrastructure operations 1</t>
+          <t>Infrastructure operations 4</t>
         </is>
       </c>
       <c r="C579" t="n">
@@ -9138,7 +9138,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>Infrastructure operations 3</t>
+          <t>Infrastructure operations 1</t>
         </is>
       </c>
       <c r="C581" t="n">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Infrastructure operations 4</t>
+          <t>Infrastructure operations 3</t>
         </is>
       </c>
       <c r="C582" t="n">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Information security 5</t>
+          <t>Information security 7</t>
         </is>
       </c>
       <c r="C587" t="n">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Information security 2</t>
+          <t>Information security 3</t>
         </is>
       </c>
       <c r="C588" t="n">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Information security 6</t>
+          <t>Information security 4</t>
         </is>
       </c>
       <c r="C589" t="n">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Information security 4</t>
+          <t>Information security 6</t>
         </is>
       </c>
       <c r="C590" t="n">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Information security 7</t>
+          <t>Information security 2</t>
         </is>
       </c>
       <c r="C591" t="n">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Information security 3</t>
+          <t>Information security 5</t>
         </is>
       </c>
       <c r="C592" t="n">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Network design 2</t>
+          <t>Network design 3</t>
         </is>
       </c>
       <c r="C593" t="n">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Network design 3</t>
+          <t>Network design 2</t>
         </is>
       </c>
       <c r="C594" t="n">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Customer service support 2</t>
+          <t>Customer service support 1</t>
         </is>
       </c>
       <c r="C595" t="n">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Customer service support 1</t>
+          <t>Customer service support 2</t>
         </is>
       </c>
       <c r="C596" t="n">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Network design 2</t>
+          <t>Network design 3</t>
         </is>
       </c>
       <c r="C597" t="n">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Network design 3</t>
+          <t>Network design 2</t>
         </is>
       </c>
       <c r="C598" t="n">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Marketing management 6</t>
+          <t>Marketing management 5</t>
         </is>
       </c>
       <c r="C605" t="n">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Marketing management 5</t>
+          <t>Marketing management 6</t>
         </is>
       </c>
       <c r="C606" t="n">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Storage management 4</t>
+          <t>Storage management 3</t>
         </is>
       </c>
       <c r="C608" t="n">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Storage management 3</t>
+          <t>Storage management 4</t>
         </is>
       </c>
       <c r="C609" t="n">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Service level management 3</t>
+          <t>Service level management 2</t>
         </is>
       </c>
       <c r="C611" t="n">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Service level management 2</t>
+          <t>Service level management 3</t>
         </is>
       </c>
       <c r="C612" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Programming/software development 2</t>
+          <t>Programming/software development 3</t>
         </is>
       </c>
       <c r="C613" t="n">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Programming/software development 3</t>
+          <t>Programming/software development 2</t>
         </is>
       </c>
       <c r="C614" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Solution architecture 4</t>
+          <t>Solution architecture 5</t>
         </is>
       </c>
       <c r="C616" t="n">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Solution architecture 5</t>
+          <t>Solution architecture 4</t>
         </is>
       </c>
       <c r="C617" t="n">
@@ -9723,7 +9723,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C620" t="n">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C621" t="n">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Network support 5</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C622" t="n">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Network support 3</t>
+          <t>Network support 5</t>
         </is>
       </c>
       <c r="C623" t="n">
@@ -9783,7 +9783,7 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 3</t>
         </is>
       </c>
       <c r="C624" t="n">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>System software administration 3</t>
+          <t>System software administration 2</t>
         </is>
       </c>
       <c r="C627" t="n">
@@ -9843,7 +9843,7 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>System software administration 2</t>
+          <t>System software administration 3</t>
         </is>
       </c>
       <c r="C628" t="n">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>Network design 2</t>
+          <t>Network design 3</t>
         </is>
       </c>
       <c r="C630" t="n">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Network design 3</t>
+          <t>Network design 2</t>
         </is>
       </c>
       <c r="C631" t="n">
@@ -9918,7 +9918,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 2</t>
         </is>
       </c>
       <c r="C633" t="n">
@@ -9933,7 +9933,7 @@
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Penetration testing 2</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C634" t="n">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Security operations 1</t>
+          <t>Security operations 2</t>
         </is>
       </c>
       <c r="C635" t="n">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Security operations 2</t>
+          <t>Security operations 1</t>
         </is>
       </c>
       <c r="C636" t="n">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Penetration testing 5</t>
+          <t>Penetration testing 4</t>
         </is>
       </c>
       <c r="C638" t="n">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 2</t>
         </is>
       </c>
       <c r="C639" t="n">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Penetration testing 2</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C640" t="n">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Penetration testing 4</t>
+          <t>Penetration testing 5</t>
         </is>
       </c>
       <c r="C641" t="n">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 4</t>
         </is>
       </c>
       <c r="C646" t="n">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Penetration testing 4</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C648" t="n">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Vulnerability assessment 4</t>
+          <t>Vulnerability assessment 3</t>
         </is>
       </c>
       <c r="C650" t="n">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Vulnerability assessment 3</t>
+          <t>Vulnerability assessment 4</t>
         </is>
       </c>
       <c r="C651" t="n">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 4</t>
         </is>
       </c>
       <c r="C652" t="n">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Penetration testing 4</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C654" t="n">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 2</t>
         </is>
       </c>
       <c r="C655" t="n">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Penetration testing 2</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C656" t="n">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Penetration testing 5</t>
+          <t>Penetration testing 4</t>
         </is>
       </c>
       <c r="C657" t="n">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 2</t>
         </is>
       </c>
       <c r="C658" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Penetration testing 2</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C659" t="n">
@@ -10323,7 +10323,7 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Penetration testing 4</t>
+          <t>Penetration testing 5</t>
         </is>
       </c>
       <c r="C660" t="n">
@@ -10458,7 +10458,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Systems installation and removal 4</t>
+          <t>Systems installation and removal 2</t>
         </is>
       </c>
       <c r="C669" t="n">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Systems installation and removal 3</t>
+          <t>Systems installation and removal 1</t>
         </is>
       </c>
       <c r="C670" t="n">
@@ -10488,7 +10488,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>Systems installation and removal 2</t>
+          <t>Systems installation and removal 3</t>
         </is>
       </c>
       <c r="C671" t="n">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Systems installation and removal 1</t>
+          <t>Systems installation and removal 4</t>
         </is>
       </c>
       <c r="C672" t="n">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>Problem management 2</t>
+          <t>Problem management 5</t>
         </is>
       </c>
       <c r="C673" t="n">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Problem management 3</t>
+          <t>Problem management 2</t>
         </is>
       </c>
       <c r="C674" t="n">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>Problem management 5</t>
+          <t>Problem management 4</t>
         </is>
       </c>
       <c r="C675" t="n">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Problem management 4</t>
+          <t>Problem management 3</t>
         </is>
       </c>
       <c r="C676" t="n">
@@ -10593,7 +10593,7 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>Problem management 3</t>
+          <t>Problem management 4</t>
         </is>
       </c>
       <c r="C678" t="n">
@@ -10608,7 +10608,7 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>Problem management 4</t>
+          <t>Problem management 3</t>
         </is>
       </c>
       <c r="C679" t="n">
@@ -10653,7 +10653,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>Asset management 2</t>
+          <t>Asset management 3</t>
         </is>
       </c>
       <c r="C682" t="n">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>Asset management 3</t>
+          <t>Asset management 2</t>
         </is>
       </c>
       <c r="C683" t="n">
@@ -10698,7 +10698,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>Asset management 2</t>
+          <t>Asset management 5</t>
         </is>
       </c>
       <c r="C685" t="n">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>Asset management 3</t>
+          <t>Asset management 4</t>
         </is>
       </c>
       <c r="C686" t="n">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>Asset management 4</t>
+          <t>Asset management 3</t>
         </is>
       </c>
       <c r="C687" t="n">
@@ -10743,7 +10743,7 @@
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>Asset management 5</t>
+          <t>Asset management 2</t>
         </is>
       </c>
       <c r="C688" t="n">
@@ -10773,7 +10773,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>Capacity management 2</t>
+          <t>Capacity management 3</t>
         </is>
       </c>
       <c r="C690" t="n">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>Capacity management 3</t>
+          <t>Capacity management 2</t>
         </is>
       </c>
       <c r="C691" t="n">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>Contract management 3</t>
+          <t>Contract management 4</t>
         </is>
       </c>
       <c r="C692" t="n">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>Contract management 2</t>
+          <t>Contract management 3</t>
         </is>
       </c>
       <c r="C693" t="n">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>Contract management 4</t>
+          <t>Contract management 2</t>
         </is>
       </c>
       <c r="C694" t="n">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>Business intelligence 4</t>
+          <t>Business intelligence 3</t>
         </is>
       </c>
       <c r="C696" t="n">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>Business intelligence 3</t>
+          <t>Business intelligence 4</t>
         </is>
       </c>
       <c r="C697" t="n">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>Systems and software lifecycle engineering 4</t>
+          <t>Systems and software lifecycle engineering 3</t>
         </is>
       </c>
       <c r="C701" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>Systems and software lifecycle engineering 3</t>
+          <t>Systems and software lifecycle engineering 5</t>
         </is>
       </c>
       <c r="C702" t="n">
@@ -10968,7 +10968,7 @@
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>Systems and software lifecycle engineering 5</t>
+          <t>Systems and software lifecycle engineering 4</t>
         </is>
       </c>
       <c r="C703" t="n">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>Systems and software lifecycle engineering 6</t>
+          <t>Systems and software lifecycle engineering 3</t>
         </is>
       </c>
       <c r="C705" t="n">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>Systems and software lifecycle engineering 4</t>
+          <t>Systems and software lifecycle engineering 6</t>
         </is>
       </c>
       <c r="C706" t="n">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>Systems and software lifecycle engineering 3</t>
+          <t>Systems and software lifecycle engineering 5</t>
         </is>
       </c>
       <c r="C707" t="n">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>Systems and software lifecycle engineering 5</t>
+          <t>Systems and software lifecycle engineering 4</t>
         </is>
       </c>
       <c r="C708" t="n">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>User experience evaluation 3</t>
+          <t>User experience evaluation 2</t>
         </is>
       </c>
       <c r="C709" t="n">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>User experience evaluation 2</t>
+          <t>User experience evaluation 4</t>
         </is>
       </c>
       <c r="C711" t="n">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>User experience evaluation 4</t>
+          <t>User experience evaluation 3</t>
         </is>
       </c>
       <c r="C712" t="n">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>Programming/software development 2</t>
+          <t>Programming/software development 3</t>
         </is>
       </c>
       <c r="C714" t="n">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>Programming/software development 3</t>
+          <t>Programming/software development 2</t>
         </is>
       </c>
       <c r="C715" t="n">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>Hardware design 4</t>
+          <t>Hardware design 3</t>
         </is>
       </c>
       <c r="C716" t="n">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>Hardware design 2</t>
+          <t>Hardware design 4</t>
         </is>
       </c>
       <c r="C717" t="n">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>Hardware design 5</t>
+          <t>Hardware design 2</t>
         </is>
       </c>
       <c r="C718" t="n">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>Hardware design 3</t>
+          <t>Hardware design 5</t>
         </is>
       </c>
       <c r="C719" t="n">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>Hardware design 3</t>
+          <t>Hardware design 4</t>
         </is>
       </c>
       <c r="C720" t="n">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>Hardware design 6</t>
+          <t>Hardware design 2</t>
         </is>
       </c>
       <c r="C721" t="n">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>Hardware design 4</t>
+          <t>Hardware design 5</t>
         </is>
       </c>
       <c r="C722" t="n">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>Hardware design 2</t>
+          <t>Hardware design 3</t>
         </is>
       </c>
       <c r="C723" t="n">
@@ -11283,7 +11283,7 @@
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>Hardware design 5</t>
+          <t>Hardware design 6</t>
         </is>
       </c>
       <c r="C724" t="n">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>Hardware design 4</t>
+          <t>Hardware design 3</t>
         </is>
       </c>
       <c r="C725" t="n">
@@ -11313,7 +11313,7 @@
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>Hardware design 2</t>
+          <t>Hardware design 4</t>
         </is>
       </c>
       <c r="C726" t="n">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>Hardware design 3</t>
+          <t>Hardware design 2</t>
         </is>
       </c>
       <c r="C727" t="n">
@@ -11343,7 +11343,7 @@
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>Hardware design 2</t>
+          <t>Hardware design 3</t>
         </is>
       </c>
       <c r="C728" t="n">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>Hardware design 3</t>
+          <t>Hardware design 2</t>
         </is>
       </c>
       <c r="C729" t="n">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>Sales support 2</t>
+          <t>Sales support 1</t>
         </is>
       </c>
       <c r="C732" t="n">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>Sales support 1</t>
+          <t>Sales support 2</t>
         </is>
       </c>
       <c r="C733" t="n">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>Sales support 3</t>
+          <t>Sales support 5</t>
         </is>
       </c>
       <c r="C734" t="n">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Sales support 5</t>
+          <t>Sales support 3</t>
         </is>
       </c>
       <c r="C735" t="n">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>Audit 6</t>
+          <t>Audit 3</t>
         </is>
       </c>
       <c r="C737" t="n">
@@ -11493,7 +11493,7 @@
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>Audit 3</t>
+          <t>Audit 6</t>
         </is>
       </c>
       <c r="C738" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>Audit 6</t>
+          <t>Audit 3</t>
         </is>
       </c>
       <c r="C745" t="n">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Audit 3</t>
+          <t>Audit 6</t>
         </is>
       </c>
       <c r="C746" t="n">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>Audit 4</t>
+          <t>Audit 2</t>
         </is>
       </c>
       <c r="C749" t="n">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>Audit 2</t>
+          <t>Audit 4</t>
         </is>
       </c>
       <c r="C750" t="n">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>Audit 5</t>
+          <t>Audit 3</t>
         </is>
       </c>
       <c r="C751" t="n">
@@ -11703,7 +11703,7 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>Audit 3</t>
+          <t>Audit 5</t>
         </is>
       </c>
       <c r="C752" t="n">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>Deployment 5</t>
+          <t>Deployment 3</t>
         </is>
       </c>
       <c r="C753" t="n">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>Deployment 3</t>
+          <t>Deployment 2</t>
         </is>
       </c>
       <c r="C754" t="n">
@@ -11748,7 +11748,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>Deployment 2</t>
+          <t>Deployment 4</t>
         </is>
       </c>
       <c r="C755" t="n">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>Deployment 4</t>
+          <t>Deployment 5</t>
         </is>
       </c>
       <c r="C756" t="n">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>Software design 3</t>
+          <t>Software design 4</t>
         </is>
       </c>
       <c r="C763" t="n">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>Software design 6</t>
+          <t>Software design 2</t>
         </is>
       </c>
       <c r="C764" t="n">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>Software design 2</t>
+          <t>Software design 6</t>
         </is>
       </c>
       <c r="C766" t="n">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Software design 4</t>
+          <t>Software design 3</t>
         </is>
       </c>
       <c r="C767" t="n">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Software design 3</t>
+          <t>Software design 4</t>
         </is>
       </c>
       <c r="C768" t="n">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>Software design 4</t>
+          <t>Software design 3</t>
         </is>
       </c>
       <c r="C770" t="n">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>User experience design 6</t>
+          <t>User experience design 4</t>
         </is>
       </c>
       <c r="C771" t="n">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>User experience design 5</t>
+          <t>User experience design 6</t>
         </is>
       </c>
       <c r="C772" t="n">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>User experience design 4</t>
+          <t>User experience design 5</t>
         </is>
       </c>
       <c r="C773" t="n">
@@ -12033,7 +12033,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>User experience design 2</t>
+          <t>User experience design 3</t>
         </is>
       </c>
       <c r="C774" t="n">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>User experience design 3</t>
+          <t>User experience design 2</t>
         </is>
       </c>
       <c r="C775" t="n">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>Identity and access management 3</t>
+          <t>Identity and access management 4</t>
         </is>
       </c>
       <c r="C778" t="n">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>Identity and access management 4</t>
+          <t>Identity and access management 3</t>
         </is>
       </c>
       <c r="C780" t="n">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>Enterprise and business architecture 6</t>
+          <t>Enterprise and business architecture 5</t>
         </is>
       </c>
       <c r="C782" t="n">
@@ -12168,7 +12168,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>Enterprise and business architecture 5</t>
+          <t>Enterprise and business architecture 6</t>
         </is>
       </c>
       <c r="C783" t="n">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>Content design and authoring 2</t>
+          <t>Content design and authoring 4</t>
         </is>
       </c>
       <c r="C784" t="n">
@@ -12228,7 +12228,7 @@
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>Content design and authoring 4</t>
+          <t>Content design and authoring 3</t>
         </is>
       </c>
       <c r="C787" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>Content design and authoring 3</t>
+          <t>Content design and authoring 6</t>
         </is>
       </c>
       <c r="C788" t="n">
@@ -12258,7 +12258,7 @@
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>Content design and authoring 6</t>
+          <t>Content design and authoring 2</t>
         </is>
       </c>
       <c r="C789" t="n">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>Content design and authoring 2</t>
+          <t>Content design and authoring 4</t>
         </is>
       </c>
       <c r="C790" t="n">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>Content design and authoring 4</t>
+          <t>Content design and authoring 3</t>
         </is>
       </c>
       <c r="C793" t="n">
@@ -12333,7 +12333,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>Content design and authoring 3</t>
+          <t>Content design and authoring 2</t>
         </is>
       </c>
       <c r="C794" t="n">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>Configuration management 2</t>
+          <t>Configuration management 3</t>
         </is>
       </c>
       <c r="C797" t="n">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>Configuration management 3</t>
+          <t>Configuration management 2</t>
         </is>
       </c>
       <c r="C798" t="n">
@@ -12423,7 +12423,7 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>Configuration management 5</t>
+          <t>Configuration management 3</t>
         </is>
       </c>
       <c r="C800" t="n">
@@ -12438,7 +12438,7 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>Configuration management 4</t>
+          <t>Configuration management 2</t>
         </is>
       </c>
       <c r="C801" t="n">
@@ -12453,7 +12453,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>Configuration management 2</t>
+          <t>Configuration management 5</t>
         </is>
       </c>
       <c r="C802" t="n">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>Configuration management 3</t>
+          <t>Configuration management 4</t>
         </is>
       </c>
       <c r="C803" t="n">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>Network support 5</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C804" t="n">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>Network support 3</t>
+          <t>Network support 5</t>
         </is>
       </c>
       <c r="C805" t="n">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 3</t>
         </is>
       </c>
       <c r="C806" t="n">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>User acceptance testing 6</t>
+          <t>User acceptance testing 3</t>
         </is>
       </c>
       <c r="C812" t="n">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>User acceptance testing 3</t>
+          <t>User acceptance testing 6</t>
         </is>
       </c>
       <c r="C814" t="n">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>User acceptance testing 2</t>
+          <t>User acceptance testing 5</t>
         </is>
       </c>
       <c r="C816" t="n">
@@ -12693,7 +12693,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>User acceptance testing 5</t>
+          <t>User acceptance testing 2</t>
         </is>
       </c>
       <c r="C818" t="n">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>Systems integration and build 4</t>
+          <t>Systems integration and build 3</t>
         </is>
       </c>
       <c r="C820" t="n">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>Systems integration and build 3</t>
+          <t>Systems integration and build 4</t>
         </is>
       </c>
       <c r="C822" t="n">
@@ -12768,7 +12768,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>User acceptance testing 2</t>
+          <t>User acceptance testing 3</t>
         </is>
       </c>
       <c r="C823" t="n">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>User acceptance testing 3</t>
+          <t>User acceptance testing 2</t>
         </is>
       </c>
       <c r="C824" t="n">
@@ -12828,7 +12828,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>User experience design 6</t>
+          <t>User experience design 4</t>
         </is>
       </c>
       <c r="C827" t="n">
@@ -12843,7 +12843,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>User experience design 5</t>
+          <t>User experience design 6</t>
         </is>
       </c>
       <c r="C828" t="n">
@@ -12858,7 +12858,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>User experience design 4</t>
+          <t>User experience design 5</t>
         </is>
       </c>
       <c r="C829" t="n">
@@ -12873,7 +12873,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>User experience design 2</t>
+          <t>User experience design 3</t>
         </is>
       </c>
       <c r="C830" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>User experience design 3</t>
+          <t>User experience design 2</t>
         </is>
       </c>
       <c r="C831" t="n">
@@ -12918,7 +12918,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C833" t="n">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>Network support 4</t>
+          <t>Network support 3</t>
         </is>
       </c>
       <c r="C834" t="n">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>Network support 3</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C835" t="n">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 4</t>
         </is>
       </c>
       <c r="C836" t="n">
@@ -12978,7 +12978,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>Network design 2</t>
+          <t>Network design 3</t>
         </is>
       </c>
       <c r="C837" t="n">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>Network design 5</t>
+          <t>Network design 2</t>
         </is>
       </c>
       <c r="C838" t="n">
@@ -13008,7 +13008,7 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>Network design 3</t>
+          <t>Network design 4</t>
         </is>
       </c>
       <c r="C839" t="n">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>Network design 4</t>
+          <t>Network design 5</t>
         </is>
       </c>
       <c r="C840" t="n">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>Network design 2</t>
+          <t>Network design 3</t>
         </is>
       </c>
       <c r="C841" t="n">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>Network design 5</t>
+          <t>Network design 2</t>
         </is>
       </c>
       <c r="C842" t="n">
@@ -13068,7 +13068,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>Network design 3</t>
+          <t>Network design 4</t>
         </is>
       </c>
       <c r="C843" t="n">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>Network design 4</t>
+          <t>Network design 5</t>
         </is>
       </c>
       <c r="C844" t="n">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C845" t="n">
@@ -13113,7 +13113,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>Network support 4</t>
+          <t>Network support 3</t>
         </is>
       </c>
       <c r="C846" t="n">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>Network support 3</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C847" t="n">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 4</t>
         </is>
       </c>
       <c r="C848" t="n">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C849" t="n">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C850" t="n">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>Network support 5</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C851" t="n">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>Network support 3</t>
+          <t>Network support 5</t>
         </is>
       </c>
       <c r="C852" t="n">
@@ -13218,7 +13218,7 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 3</t>
         </is>
       </c>
       <c r="C853" t="n">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C858" t="n">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C859" t="n">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>Network design 2</t>
+          <t>Network design 3</t>
         </is>
       </c>
       <c r="C861" t="n">
@@ -13353,7 +13353,7 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>Network design 5</t>
+          <t>Network design 2</t>
         </is>
       </c>
       <c r="C862" t="n">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>Network design 3</t>
+          <t>Network design 4</t>
         </is>
       </c>
       <c r="C863" t="n">
@@ -13383,7 +13383,7 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>Network design 4</t>
+          <t>Network design 5</t>
         </is>
       </c>
       <c r="C864" t="n">
@@ -13398,7 +13398,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C865" t="n">
@@ -13413,7 +13413,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>Network support 4</t>
+          <t>Network support 3</t>
         </is>
       </c>
       <c r="C866" t="n">
@@ -13428,7 +13428,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>Network support 3</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C867" t="n">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 4</t>
         </is>
       </c>
       <c r="C868" t="n">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C869" t="n">
@@ -13473,7 +13473,7 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C870" t="n">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>Network support 5</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C871" t="n">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>Network support 3</t>
+          <t>Network support 5</t>
         </is>
       </c>
       <c r="C872" t="n">
@@ -13518,7 +13518,7 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 3</t>
         </is>
       </c>
       <c r="C873" t="n">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>Network design 2</t>
+          <t>Network design 5</t>
         </is>
       </c>
       <c r="C878" t="n">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>Network design 5</t>
+          <t>Network design 2</t>
         </is>
       </c>
       <c r="C880" t="n">
@@ -13638,7 +13638,7 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>Network design 6</t>
+          <t>Network design 4</t>
         </is>
       </c>
       <c r="C881" t="n">
@@ -13653,7 +13653,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>Network design 4</t>
+          <t>Network design 6</t>
         </is>
       </c>
       <c r="C882" t="n">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Network support 2</t>
+          <t>Network support 1</t>
         </is>
       </c>
       <c r="C883" t="n">
@@ -13698,7 +13698,7 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>Network support 1</t>
+          <t>Network support 2</t>
         </is>
       </c>
       <c r="C885" t="n">
@@ -13713,7 +13713,7 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>Network design 2</t>
+          <t>Network design 3</t>
         </is>
       </c>
       <c r="C886" t="n">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>Network design 3</t>
+          <t>Network design 2</t>
         </is>
       </c>
       <c r="C887" t="n">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>Customer service support 2</t>
+          <t>Customer service support 1</t>
         </is>
       </c>
       <c r="C889" t="n">
@@ -13773,7 +13773,7 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>Customer service support 1</t>
+          <t>Customer service support 2</t>
         </is>
       </c>
       <c r="C890" t="n">
@@ -13833,7 +13833,7 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>Programming/software development 2</t>
+          <t>Programming/software development 3</t>
         </is>
       </c>
       <c r="C894" t="n">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>Programming/software development 3</t>
+          <t>Programming/software development 2</t>
         </is>
       </c>
       <c r="C895" t="n">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>Programming/software development 2</t>
+          <t>Programming/software development 3</t>
         </is>
       </c>
       <c r="C896" t="n">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>Programming/software development 3</t>
+          <t>Programming/software development 2</t>
         </is>
       </c>
       <c r="C898" t="n">
@@ -13923,7 +13923,7 @@
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>Programming/software development 3</t>
+          <t>Programming/software development 5</t>
         </is>
       </c>
       <c r="C900" t="n">
@@ -13938,7 +13938,7 @@
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>Programming/software development 5</t>
+          <t>Programming/software development 3</t>
         </is>
       </c>
       <c r="C901" t="n">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>Budgeting and forecasting 4</t>
+          <t>Budgeting and forecasting 3</t>
         </is>
       </c>
       <c r="C904" t="n">
@@ -14013,7 +14013,7 @@
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>Budgeting and forecasting 3</t>
+          <t>Budgeting and forecasting 4</t>
         </is>
       </c>
       <c r="C906" t="n">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>Database design 2</t>
+          <t>Database design 3</t>
         </is>
       </c>
       <c r="C907" t="n">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>Database design 3</t>
+          <t>Database design 2</t>
         </is>
       </c>
       <c r="C908" t="n">
@@ -14058,7 +14058,7 @@
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>Portfolio management 5</t>
+          <t>Portfolio management 6</t>
         </is>
       </c>
       <c r="C909" t="n">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>Portfolio management 6</t>
+          <t>Portfolio management 5</t>
         </is>
       </c>
       <c r="C910" t="n">
@@ -14088,7 +14088,7 @@
       </c>
       <c r="B911" t="inlineStr">
         <is>
-          <t>Consultancy 6</t>
+          <t>Consultancy 4</t>
         </is>
       </c>
       <c r="C911" t="n">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>Consultancy 4</t>
+          <t>Consultancy 6</t>
         </is>
       </c>
       <c r="C912" t="n">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="B915" t="inlineStr">
         <is>
-          <t>User acceptance testing 2</t>
+          <t>User acceptance testing 3</t>
         </is>
       </c>
       <c r="C915" t="n">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="B916" t="inlineStr">
         <is>
-          <t>User acceptance testing 3</t>
+          <t>User acceptance testing 2</t>
         </is>
       </c>
       <c r="C916" t="n">
@@ -14223,7 +14223,7 @@
       </c>
       <c r="B920" t="inlineStr">
         <is>
-          <t>Data science 5</t>
+          <t>Data science 4</t>
         </is>
       </c>
       <c r="C920" t="n">
@@ -14253,7 +14253,7 @@
       </c>
       <c r="B922" t="inlineStr">
         <is>
-          <t>Data science 4</t>
+          <t>Data science 5</t>
         </is>
       </c>
       <c r="C922" t="n">
@@ -14373,7 +14373,7 @@
       </c>
       <c r="B930" t="inlineStr">
         <is>
-          <t>Functional testing 2</t>
+          <t>Functional testing 3</t>
         </is>
       </c>
       <c r="C930" t="n">
@@ -14403,7 +14403,7 @@
       </c>
       <c r="B932" t="inlineStr">
         <is>
-          <t>Functional testing 3</t>
+          <t>Functional testing 4</t>
         </is>
       </c>
       <c r="C932" t="n">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>Functional testing 4</t>
+          <t>Functional testing 2</t>
         </is>
       </c>
       <c r="C933" t="n">
@@ -14433,7 +14433,7 @@
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>Functional testing 6</t>
+          <t>Functional testing 3</t>
         </is>
       </c>
       <c r="C934" t="n">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="B935" t="inlineStr">
         <is>
-          <t>Functional testing 4</t>
+          <t>Functional testing 6</t>
         </is>
       </c>
       <c r="C935" t="n">
@@ -14463,7 +14463,7 @@
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>Functional testing 3</t>
+          <t>Functional testing 1</t>
         </is>
       </c>
       <c r="C936" t="n">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>Functional testing 2</t>
+          <t>Functional testing 4</t>
         </is>
       </c>
       <c r="C937" t="n">
@@ -14493,7 +14493,7 @@
       </c>
       <c r="B938" t="inlineStr">
         <is>
-          <t>Functional testing 5</t>
+          <t>Functional testing 2</t>
         </is>
       </c>
       <c r="C938" t="n">
@@ -14508,7 +14508,7 @@
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>Functional testing 1</t>
+          <t>Functional testing 5</t>
         </is>
       </c>
       <c r="C939" t="n">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="B940" t="inlineStr">
         <is>
-          <t>Functional testing 2</t>
+          <t>Functional testing 3</t>
         </is>
       </c>
       <c r="C940" t="n">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="B942" t="inlineStr">
         <is>
-          <t>Functional testing 3</t>
+          <t>Functional testing 2</t>
         </is>
       </c>
       <c r="C942" t="n">
@@ -14568,7 +14568,7 @@
       </c>
       <c r="B943" t="inlineStr">
         <is>
-          <t>Functional testing 4</t>
+          <t>Functional testing 3</t>
         </is>
       </c>
       <c r="C943" t="n">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="B944" t="inlineStr">
         <is>
-          <t>Functional testing 3</t>
+          <t>Functional testing 1</t>
         </is>
       </c>
       <c r="C944" t="n">
@@ -14598,7 +14598,7 @@
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>Functional testing 2</t>
+          <t>Functional testing 4</t>
         </is>
       </c>
       <c r="C945" t="n">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>Functional testing 5</t>
+          <t>Functional testing 2</t>
         </is>
       </c>
       <c r="C946" t="n">
@@ -14628,7 +14628,7 @@
       </c>
       <c r="B947" t="inlineStr">
         <is>
-          <t>Functional testing 1</t>
+          <t>Functional testing 5</t>
         </is>
       </c>
       <c r="C947" t="n">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="B949" t="inlineStr">
         <is>
-          <t>Functional testing 2</t>
+          <t>Functional testing 1</t>
         </is>
       </c>
       <c r="C949" t="n">
@@ -14673,7 +14673,7 @@
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>Functional testing 1</t>
+          <t>Functional testing 2</t>
         </is>
       </c>
       <c r="C950" t="n">
@@ -14688,7 +14688,7 @@
       </c>
       <c r="B951" t="inlineStr">
         <is>
-          <t>Non-functional testing 1</t>
+          <t>Non-functional testing 4</t>
         </is>
       </c>
       <c r="C951" t="n">
@@ -14703,7 +14703,7 @@
       </c>
       <c r="B952" t="inlineStr">
         <is>
-          <t>Non-functional testing 5</t>
+          <t>Non-functional testing 3</t>
         </is>
       </c>
       <c r="C952" t="n">
@@ -14718,7 +14718,7 @@
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>Non-functional testing 2</t>
+          <t>Non-functional testing 5</t>
         </is>
       </c>
       <c r="C953" t="n">
@@ -14733,7 +14733,7 @@
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>Non-functional testing 3</t>
+          <t>Non-functional testing 1</t>
         </is>
       </c>
       <c r="C954" t="n">
@@ -14748,7 +14748,7 @@
       </c>
       <c r="B955" t="inlineStr">
         <is>
-          <t>Non-functional testing 4</t>
+          <t>Non-functional testing 2</t>
         </is>
       </c>
       <c r="C955" t="n">
@@ -14763,7 +14763,7 @@
       </c>
       <c r="B956" t="inlineStr">
         <is>
-          <t>Non-functional testing 6</t>
+          <t>Non-functional testing 4</t>
         </is>
       </c>
       <c r="C956" t="n">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>Non-functional testing 1</t>
+          <t>Non-functional testing 3</t>
         </is>
       </c>
       <c r="C957" t="n">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="B959" t="inlineStr">
         <is>
-          <t>Non-functional testing 2</t>
+          <t>Non-functional testing 1</t>
         </is>
       </c>
       <c r="C959" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="B960" t="inlineStr">
         <is>
-          <t>Non-functional testing 3</t>
+          <t>Non-functional testing 6</t>
         </is>
       </c>
       <c r="C960" t="n">
@@ -14838,7 +14838,7 @@
       </c>
       <c r="B961" t="inlineStr">
         <is>
-          <t>Non-functional testing 4</t>
+          <t>Non-functional testing 2</t>
         </is>
       </c>
       <c r="C961" t="n">
@@ -14853,7 +14853,7 @@
       </c>
       <c r="B962" t="inlineStr">
         <is>
-          <t>Non-functional testing 1</t>
+          <t>Non-functional testing 4</t>
         </is>
       </c>
       <c r="C962" t="n">
@@ -14868,7 +14868,7 @@
       </c>
       <c r="B963" t="inlineStr">
         <is>
-          <t>Non-functional testing 4</t>
+          <t>Non-functional testing 1</t>
         </is>
       </c>
       <c r="C963" t="n">
@@ -14883,7 +14883,7 @@
       </c>
       <c r="B964" t="inlineStr">
         <is>
-          <t>Non-functional testing 2</t>
+          <t>Non-functional testing 3</t>
         </is>
       </c>
       <c r="C964" t="n">
@@ -14898,7 +14898,7 @@
       </c>
       <c r="B965" t="inlineStr">
         <is>
-          <t>Non-functional testing 3</t>
+          <t>Non-functional testing 2</t>
         </is>
       </c>
       <c r="C965" t="n">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="B970" t="inlineStr">
         <is>
-          <t>Infrastructure operations 1</t>
+          <t>Infrastructure operations 2</t>
         </is>
       </c>
       <c r="C970" t="n">
@@ -14988,7 +14988,7 @@
       </c>
       <c r="B971" t="inlineStr">
         <is>
-          <t>Infrastructure operations 2</t>
+          <t>Infrastructure operations 1</t>
         </is>
       </c>
       <c r="C971" t="n">
@@ -15003,7 +15003,7 @@
       </c>
       <c r="B972" t="inlineStr">
         <is>
-          <t>Deployment 5</t>
+          <t>Deployment 3</t>
         </is>
       </c>
       <c r="C972" t="n">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="B973" t="inlineStr">
         <is>
-          <t>Deployment 3</t>
+          <t>Deployment 2</t>
         </is>
       </c>
       <c r="C973" t="n">
@@ -15033,7 +15033,7 @@
       </c>
       <c r="B974" t="inlineStr">
         <is>
-          <t>Deployment 2</t>
+          <t>Deployment 4</t>
         </is>
       </c>
       <c r="C974" t="n">
@@ -15048,7 +15048,7 @@
       </c>
       <c r="B975" t="inlineStr">
         <is>
-          <t>Deployment 4</t>
+          <t>Deployment 5</t>
         </is>
       </c>
       <c r="C975" t="n">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="B976" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 2</t>
         </is>
       </c>
       <c r="C976" t="n">
@@ -15078,7 +15078,7 @@
       </c>
       <c r="B977" t="inlineStr">
         <is>
-          <t>Penetration testing 2</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C977" t="n">
@@ -15108,7 +15108,7 @@
       </c>
       <c r="B979" t="inlineStr">
         <is>
-          <t>Penetration testing 5</t>
+          <t>Penetration testing 4</t>
         </is>
       </c>
       <c r="C979" t="n">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="B980" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 2</t>
         </is>
       </c>
       <c r="C980" t="n">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="B981" t="inlineStr">
         <is>
-          <t>Penetration testing 2</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C981" t="n">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="B982" t="inlineStr">
         <is>
-          <t>Penetration testing 4</t>
+          <t>Penetration testing 5</t>
         </is>
       </c>
       <c r="C982" t="n">
@@ -15168,7 +15168,7 @@
       </c>
       <c r="B983" t="inlineStr">
         <is>
-          <t>Penetration testing 3</t>
+          <t>Penetration testing 4</t>
         </is>
       </c>
       <c r="C983" t="n">
@@ -15198,7 +15198,7 @@
       </c>
       <c r="B985" t="inlineStr">
         <is>
-          <t>Penetration testing 4</t>
+          <t>Penetration testing 3</t>
         </is>
       </c>
       <c r="C985" t="n">
@@ -15213,7 +15213,7 @@
       </c>
       <c r="B986" t="inlineStr">
         <is>
-          <t>Penetration testing 5</t>
+          <t>Penetration testing 2</t>
         </is>
       </c>
       <c r="C986" t="n">
@@ -15258,7 +15258,7 @@
       </c>
       <c r="B989" t="inlineStr">
         <is>
-          <t>Penetration testing 2</t>
+          <t>Penetration testing 4</t>
         </is>
       </c>
       <c r="C989" t="n">
@@ -15273,7 +15273,7 @@
       </c>
       <c r="B990" t="inlineStr">
         <is>
-          <t>Penetration testing 4</t>
+          <t>Penetration testing 5</t>
         </is>
       </c>
       <c r="C990" t="n">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="B994" t="inlineStr">
         <is>
-          <t>Storage management 4</t>
+          <t>Storage management 3</t>
         </is>
       </c>
       <c r="C994" t="n">
@@ -15348,7 +15348,7 @@
       </c>
       <c r="B995" t="inlineStr">
         <is>
-          <t>Storage management 3</t>
+          <t>Storage management 4</t>
         </is>
       </c>
       <c r="C995" t="n">
@@ -15393,7 +15393,7 @@
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>Storage management 4</t>
+          <t>Storage management 3</t>
         </is>
       </c>
       <c r="C998" t="n">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="B999" t="inlineStr">
         <is>
-          <t>Storage management 3</t>
+          <t>Storage management 4</t>
         </is>
       </c>
       <c r="C999" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="B1003" t="inlineStr">
         <is>
-          <t>Infrastructure operations 1</t>
+          <t>Infrastructure operations 4</t>
         </is>
       </c>
       <c r="C1003" t="n">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="B1005" t="inlineStr">
         <is>
-          <t>Infrastructure operations 3</t>
+          <t>Infrastructure operations 1</t>
         </is>
       </c>
       <c r="C1005" t="n">
@@ -15513,7 +15513,7 @@
       </c>
       <c r="B1006" t="inlineStr">
         <is>
-          <t>Infrastructure operations 4</t>
+          <t>Infrastructure operations 3</t>
         </is>
       </c>
       <c r="C1006" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="B1007" t="inlineStr">
         <is>
-          <t>Infrastructure operations 1</t>
+          <t>Infrastructure operations 2</t>
         </is>
       </c>
       <c r="C1007" t="n">
@@ -15543,7 +15543,7 @@
       </c>
       <c r="B1008" t="inlineStr">
         <is>
-          <t>Infrastructure operations 2</t>
+          <t>Infrastructure operations 1</t>
         </is>
       </c>
       <c r="C1008" t="n">
@@ -15558,7 +15558,7 @@
       </c>
       <c r="B1009" t="inlineStr">
         <is>
-          <t>Infrastructure operations 1</t>
+          <t>Infrastructure operations 2</t>
         </is>
       </c>
       <c r="C1009" t="n">
@@ -15573,7 +15573,7 @@
       </c>
       <c r="B1010" t="inlineStr">
         <is>
-          <t>Infrastructure operations 2</t>
+          <t>Infrastructure operations 1</t>
         </is>
       </c>
       <c r="C1010" t="n">
@@ -15663,7 +15663,7 @@
       </c>
       <c r="B1016" t="inlineStr">
         <is>
-          <t>Machine learning 2</t>
+          <t>Machine learning 3</t>
         </is>
       </c>
       <c r="C1016" t="n">
@@ -15678,7 +15678,7 @@
       </c>
       <c r="B1017" t="inlineStr">
         <is>
-          <t>Machine learning 3</t>
+          <t>Machine learning 2</t>
         </is>
       </c>
       <c r="C1017" t="n">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="B1018" t="inlineStr">
         <is>
-          <t>Machine learning 5</t>
+          <t>Machine learning 4</t>
         </is>
       </c>
       <c r="C1018" t="n">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="B1019" t="inlineStr">
         <is>
-          <t>Machine learning 4</t>
+          <t>Machine learning 5</t>
         </is>
       </c>
       <c r="C1019" t="n">
@@ -15768,7 +15768,7 @@
       </c>
       <c r="B1023" t="inlineStr">
         <is>
-          <t>Functional testing 4</t>
+          <t>Functional testing 3</t>
         </is>
       </c>
       <c r="C1023" t="n">
@@ -15783,7 +15783,7 @@
       </c>
       <c r="B1024" t="inlineStr">
         <is>
-          <t>Functional testing 3</t>
+          <t>Functional testing 1</t>
         </is>
       </c>
       <c r="C1024" t="n">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>Functional testing 2</t>
+          <t>Functional testing 4</t>
         </is>
       </c>
       <c r="C1025" t="n">
@@ -15813,7 +15813,7 @@
       </c>
       <c r="B1026" t="inlineStr">
         <is>
-          <t>Functional testing 5</t>
+          <t>Functional testing 2</t>
         </is>
       </c>
       <c r="C1026" t="n">
@@ -15828,7 +15828,7 @@
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>Functional testing 1</t>
+          <t>Functional testing 5</t>
         </is>
       </c>
       <c r="C1027" t="n">
@@ -15858,7 +15858,7 @@
       </c>
       <c r="B1029" t="inlineStr">
         <is>
-          <t>Non-functional testing 1</t>
+          <t>Non-functional testing 4</t>
         </is>
       </c>
       <c r="C1029" t="n">
@@ -15873,7 +15873,7 @@
       </c>
       <c r="B1030" t="inlineStr">
         <is>
-          <t>Non-functional testing 5</t>
+          <t>Non-functional testing 3</t>
         </is>
       </c>
       <c r="C1030" t="n">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="B1031" t="inlineStr">
         <is>
-          <t>Non-functional testing 2</t>
+          <t>Non-functional testing 5</t>
         </is>
       </c>
       <c r="C1031" t="n">
@@ -15903,7 +15903,7 @@
       </c>
       <c r="B1032" t="inlineStr">
         <is>
-          <t>Non-functional testing 3</t>
+          <t>Non-functional testing 1</t>
         </is>
       </c>
       <c r="C1032" t="n">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="B1033" t="inlineStr">
         <is>
-          <t>Non-functional testing 4</t>
+          <t>Non-functional testing 2</t>
         </is>
       </c>
       <c r="C1033" t="n">
@@ -15933,7 +15933,7 @@
       </c>
       <c r="B1034" t="inlineStr">
         <is>
-          <t>Solution architecture 4</t>
+          <t>Solution architecture 5</t>
         </is>
       </c>
       <c r="C1034" t="n">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="B1035" t="inlineStr">
         <is>
-          <t>Solution architecture 5</t>
+          <t>Solution architecture 4</t>
         </is>
       </c>
       <c r="C1035" t="n">
@@ -15963,7 +15963,7 @@
       </c>
       <c r="B1036" t="inlineStr">
         <is>
-          <t>Enterprise and business architecture 6</t>
+          <t>Enterprise and business architecture 5</t>
         </is>
       </c>
       <c r="C1036" t="n">
@@ -15978,7 +15978,7 @@
       </c>
       <c r="B1037" t="inlineStr">
         <is>
-          <t>Enterprise and business architecture 5</t>
+          <t>Enterprise and business architecture 6</t>
         </is>
       </c>
       <c r="C1037" t="n">
@@ -15993,7 +15993,7 @@
       </c>
       <c r="B1038" t="inlineStr">
         <is>
-          <t>Brand management 6</t>
+          <t>Brand management 4</t>
         </is>
       </c>
       <c r="C1038" t="n">
@@ -16008,7 +16008,7 @@
       </c>
       <c r="B1039" t="inlineStr">
         <is>
-          <t>Brand management 4</t>
+          <t>Brand management 5</t>
         </is>
       </c>
       <c r="C1039" t="n">
@@ -16023,7 +16023,7 @@
       </c>
       <c r="B1040" t="inlineStr">
         <is>
-          <t>Brand management 5</t>
+          <t>Brand management 6</t>
         </is>
       </c>
       <c r="C1040" t="n">
@@ -16038,7 +16038,7 @@
       </c>
       <c r="B1041" t="inlineStr">
         <is>
-          <t>Service level management 3</t>
+          <t>Service level management 2</t>
         </is>
       </c>
       <c r="C1041" t="n">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="B1042" t="inlineStr">
         <is>
-          <t>Service level management 2</t>
+          <t>Service level management 3</t>
         </is>
       </c>
       <c r="C1042" t="n">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>Process testing 1</t>
+          <t>Process testing 5</t>
         </is>
       </c>
       <c r="C1046" t="n">
@@ -16128,7 +16128,7 @@
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>Process testing 5</t>
+          <t>Process testing 1</t>
         </is>
       </c>
       <c r="C1047" t="n">
@@ -16233,7 +16233,7 @@
       </c>
       <c r="B1054" t="inlineStr">
         <is>
-          <t>Process testing 1</t>
+          <t>Process testing 5</t>
         </is>
       </c>
       <c r="C1054" t="n">
@@ -16248,7 +16248,7 @@
       </c>
       <c r="B1055" t="inlineStr">
         <is>
-          <t>Process testing 5</t>
+          <t>Process testing 1</t>
         </is>
       </c>
       <c r="C1055" t="n">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="B1057" t="inlineStr">
         <is>
-          <t>Process testing 6</t>
+          <t>Process testing 2</t>
         </is>
       </c>
       <c r="C1057" t="n">
@@ -16293,7 +16293,7 @@
       </c>
       <c r="B1058" t="inlineStr">
         <is>
-          <t>Process testing 2</t>
+          <t>Process testing 6</t>
         </is>
       </c>
       <c r="C1058" t="n">
@@ -16323,7 +16323,7 @@
       </c>
       <c r="B1060" t="inlineStr">
         <is>
-          <t>Real-time/embedded systems development 4</t>
+          <t>Real-time/embedded systems development 3</t>
         </is>
       </c>
       <c r="C1060" t="n">
@@ -16353,7 +16353,7 @@
       </c>
       <c r="B1062" t="inlineStr">
         <is>
-          <t>Real-time/embedded systems development 5</t>
+          <t>Real-time/embedded systems development 4</t>
         </is>
       </c>
       <c r="C1062" t="n">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="B1063" t="inlineStr">
         <is>
-          <t>Real-time/embedded systems development 3</t>
+          <t>Real-time/embedded systems development 5</t>
         </is>
       </c>
       <c r="C1063" t="n">
@@ -16383,7 +16383,7 @@
       </c>
       <c r="B1064" t="inlineStr">
         <is>
-          <t>Business process improvement 2</t>
+          <t>Business process improvement 3</t>
         </is>
       </c>
       <c r="C1064" t="n">
@@ -16398,7 +16398,7 @@
       </c>
       <c r="B1065" t="inlineStr">
         <is>
-          <t>Business process improvement 3</t>
+          <t>Business process improvement 2</t>
         </is>
       </c>
       <c r="C1065" t="n">
@@ -16428,7 +16428,7 @@
       </c>
       <c r="B1067" t="inlineStr">
         <is>
-          <t>Asset management 2</t>
+          <t>Asset management 3</t>
         </is>
       </c>
       <c r="C1067" t="n">
@@ -16443,7 +16443,7 @@
       </c>
       <c r="B1068" t="inlineStr">
         <is>
-          <t>Asset management 4</t>
+          <t>Asset management 2</t>
         </is>
       </c>
       <c r="C1068" t="n">
@@ -16473,7 +16473,7 @@
       </c>
       <c r="B1070" t="inlineStr">
         <is>
-          <t>Asset management 3</t>
+          <t>Asset management 4</t>
         </is>
       </c>
       <c r="C1070" t="n">
@@ -16518,7 +16518,7 @@
       </c>
       <c r="B1073" t="inlineStr">
         <is>
-          <t>Data engineering 5</t>
+          <t>Data engineering 2</t>
         </is>
       </c>
       <c r="C1073" t="n">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="B1074" t="inlineStr">
         <is>
-          <t>Data engineering 2</t>
+          <t>Data engineering 5</t>
         </is>
       </c>
       <c r="C1074" t="n">
@@ -16563,7 +16563,7 @@
       </c>
       <c r="B1076" t="inlineStr">
         <is>
-          <t>Customer service support 2</t>
+          <t>Customer service support 1</t>
         </is>
       </c>
       <c r="C1076" t="n">
@@ -16578,7 +16578,7 @@
       </c>
       <c r="B1077" t="inlineStr">
         <is>
-          <t>Customer service support 1</t>
+          <t>Customer service support 2</t>
         </is>
       </c>
       <c r="C1077" t="n">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="B1078" t="inlineStr">
         <is>
-          <t>Service level management 3</t>
+          <t>Service level management 7</t>
         </is>
       </c>
       <c r="C1078" t="n">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="B1079" t="inlineStr">
         <is>
-          <t>Service level management 5</t>
+          <t>Service level management 6</t>
         </is>
       </c>
       <c r="C1079" t="n">
@@ -16623,7 +16623,7 @@
       </c>
       <c r="B1080" t="inlineStr">
         <is>
-          <t>Service level management 7</t>
+          <t>Service level management 3</t>
         </is>
       </c>
       <c r="C1080" t="n">
@@ -16638,7 +16638,7 @@
       </c>
       <c r="B1081" t="inlineStr">
         <is>
-          <t>Service level management 2</t>
+          <t>Service level management 5</t>
         </is>
       </c>
       <c r="C1081" t="n">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="B1082" t="inlineStr">
         <is>
-          <t>Service level management 6</t>
+          <t>Service level management 4</t>
         </is>
       </c>
       <c r="C1082" t="n">
@@ -16668,7 +16668,7 @@
       </c>
       <c r="B1083" t="inlineStr">
         <is>
-          <t>Service level management 4</t>
+          <t>Service level management 2</t>
         </is>
       </c>
       <c r="C1083" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="B1089" t="inlineStr">
         <is>
-          <t>Data analytics 3</t>
+          <t>Data analytics 2</t>
         </is>
       </c>
       <c r="C1089" t="n">
@@ -16773,7 +16773,7 @@
       </c>
       <c r="B1090" t="inlineStr">
         <is>
-          <t>Data analytics 2</t>
+          <t>Data analytics 3</t>
         </is>
       </c>
       <c r="C1090" t="n">
@@ -16833,7 +16833,7 @@
       </c>
       <c r="B1094" t="inlineStr">
         <is>
-          <t>Data analytics 4</t>
+          <t>Data analytics 2</t>
         </is>
       </c>
       <c r="C1094" t="n">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="B1095" t="inlineStr">
         <is>
-          <t>Data analytics 3</t>
+          <t>Data analytics 4</t>
         </is>
       </c>
       <c r="C1095" t="n">
@@ -16863,7 +16863,7 @@
       </c>
       <c r="B1096" t="inlineStr">
         <is>
-          <t>Data analytics 2</t>
+          <t>Data analytics 6</t>
         </is>
       </c>
       <c r="C1096" t="n">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="B1097" t="inlineStr">
         <is>
-          <t>Data analytics 6</t>
+          <t>Data analytics 3</t>
         </is>
       </c>
       <c r="C1097" t="n">
@@ -16938,7 +16938,7 @@
       </c>
       <c r="B1101" t="inlineStr">
         <is>
-          <t>Learning and development management 3</t>
+          <t>Learning and development management 5</t>
         </is>
       </c>
       <c r="C1101" t="n">
@@ -16953,7 +16953,7 @@
       </c>
       <c r="B1102" t="inlineStr">
         <is>
-          <t>Learning and development management 4</t>
+          <t>Learning and development management 2</t>
         </is>
       </c>
       <c r="C1102" t="n">
@@ -16968,7 +16968,7 @@
       </c>
       <c r="B1103" t="inlineStr">
         <is>
-          <t>Learning and development management 6</t>
+          <t>Learning and development management 4</t>
         </is>
       </c>
       <c r="C1103" t="n">
@@ -16983,7 +16983,7 @@
       </c>
       <c r="B1104" t="inlineStr">
         <is>
-          <t>Learning and development management 2</t>
+          <t>Learning and development management 7</t>
         </is>
       </c>
       <c r="C1104" t="n">
@@ -16998,7 +16998,7 @@
       </c>
       <c r="B1105" t="inlineStr">
         <is>
-          <t>Learning and development management 5</t>
+          <t>Learning and development management 6</t>
         </is>
       </c>
       <c r="C1105" t="n">
@@ -17013,7 +17013,7 @@
       </c>
       <c r="B1106" t="inlineStr">
         <is>
-          <t>Learning and development management 7</t>
+          <t>Learning and development management 3</t>
         </is>
       </c>
       <c r="C1106" t="n">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="B1108" t="inlineStr">
         <is>
-          <t>Technology service management 6</t>
+          <t>Technology service management 5</t>
         </is>
       </c>
       <c r="C1108" t="n">
@@ -17058,7 +17058,7 @@
       </c>
       <c r="B1109" t="inlineStr">
         <is>
-          <t>Technology service management 5</t>
+          <t>Technology service management 6</t>
         </is>
       </c>
       <c r="C1109" t="n">
@@ -17073,7 +17073,7 @@
       </c>
       <c r="B1110" t="inlineStr">
         <is>
-          <t>Capacity management 2</t>
+          <t>Capacity management 3</t>
         </is>
       </c>
       <c r="C1110" t="n">
@@ -17088,7 +17088,7 @@
       </c>
       <c r="B1111" t="inlineStr">
         <is>
-          <t>Capacity management 3</t>
+          <t>Capacity management 2</t>
         </is>
       </c>
       <c r="C1111" t="n">
@@ -17103,7 +17103,7 @@
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>Security operations 1</t>
+          <t>Security operations 4</t>
         </is>
       </c>
       <c r="C1112" t="n">
@@ -17133,7 +17133,7 @@
       </c>
       <c r="B1114" t="inlineStr">
         <is>
-          <t>Security operations 4</t>
+          <t>Security operations 2</t>
         </is>
       </c>
       <c r="C1114" t="n">
@@ -17163,7 +17163,7 @@
       </c>
       <c r="B1116" t="inlineStr">
         <is>
-          <t>Security operations 2</t>
+          <t>Security operations 1</t>
         </is>
       </c>
       <c r="C1116" t="n">
@@ -17178,7 +17178,7 @@
       </c>
       <c r="B1117" t="inlineStr">
         <is>
-          <t>Infrastructure operations 1</t>
+          <t>Infrastructure operations 4</t>
         </is>
       </c>
       <c r="C1117" t="n">
@@ -17208,7 +17208,7 @@
       </c>
       <c r="B1119" t="inlineStr">
         <is>
-          <t>Infrastructure operations 3</t>
+          <t>Infrastructure operations 1</t>
         </is>
       </c>
       <c r="C1119" t="n">
@@ -17223,7 +17223,7 @@
       </c>
       <c r="B1120" t="inlineStr">
         <is>
-          <t>Infrastructure operations 4</t>
+          <t>Infrastructure operations 3</t>
         </is>
       </c>
       <c r="C1120" t="n">
@@ -17268,7 +17268,7 @@
       </c>
       <c r="B1123" t="inlineStr">
         <is>
-          <t>Knowledge management 4</t>
+          <t>Knowledge management 3</t>
         </is>
       </c>
       <c r="C1123" t="n">
@@ -17283,7 +17283,7 @@
       </c>
       <c r="B1124" t="inlineStr">
         <is>
-          <t>Knowledge management 3</t>
+          <t>Knowledge management 4</t>
         </is>
       </c>
       <c r="C1124" t="n">
@@ -17358,7 +17358,7 @@
       </c>
       <c r="B1129" t="inlineStr">
         <is>
-          <t>User research 3</t>
+          <t>User research 2</t>
         </is>
       </c>
       <c r="C1129" t="n">
@@ -17373,7 +17373,7 @@
       </c>
       <c r="B1130" t="inlineStr">
         <is>
-          <t>User research 2</t>
+          <t>User research 3</t>
         </is>
       </c>
       <c r="C1130" t="n">
@@ -17388,7 +17388,7 @@
       </c>
       <c r="B1131" t="inlineStr">
         <is>
-          <t>User research 3</t>
+          <t>User research 2</t>
         </is>
       </c>
       <c r="C1131" t="n">
@@ -17418,7 +17418,7 @@
       </c>
       <c r="B1133" t="inlineStr">
         <is>
-          <t>User research 2</t>
+          <t>User research 3</t>
         </is>
       </c>
       <c r="C1133" t="n">
@@ -17433,7 +17433,7 @@
       </c>
       <c r="B1134" t="inlineStr">
         <is>
-          <t>Systems integration and build 4</t>
+          <t>Systems integration and build 3</t>
         </is>
       </c>
       <c r="C1134" t="n">
@@ -17463,7 +17463,7 @@
       </c>
       <c r="B1136" t="inlineStr">
         <is>
-          <t>Systems integration and build 3</t>
+          <t>Systems integration and build 4</t>
         </is>
       </c>
       <c r="C1136" t="n">
@@ -17508,7 +17508,7 @@
       </c>
       <c r="B1139" t="inlineStr">
         <is>
-          <t>User experience design 6</t>
+          <t>User experience design 4</t>
         </is>
       </c>
       <c r="C1139" t="n">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="B1140" t="inlineStr">
         <is>
-          <t>User experience design 5</t>
+          <t>User experience design 6</t>
         </is>
       </c>
       <c r="C1140" t="n">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>User experience design 4</t>
+          <t>User experience design 5</t>
         </is>
       </c>
       <c r="C1141" t="n">
@@ -17553,7 +17553,7 @@
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>User experience design 2</t>
+          <t>User experience design 3</t>
         </is>
       </c>
       <c r="C1142" t="n">
@@ -17568,7 +17568,7 @@
       </c>
       <c r="B1143" t="inlineStr">
         <is>
-          <t>User experience design 3</t>
+          <t>User experience design 2</t>
         </is>
       </c>
       <c r="C1143" t="n">
@@ -17598,7 +17598,7 @@
       </c>
       <c r="B1145" t="inlineStr">
         <is>
-          <t>User experience design 4</t>
+          <t>User experience design 3</t>
         </is>
       </c>
       <c r="C1145" t="n">
@@ -17613,7 +17613,7 @@
       </c>
       <c r="B1146" t="inlineStr">
         <is>
-          <t>User experience design 2</t>
+          <t>User experience design 5</t>
         </is>
       </c>
       <c r="C1146" t="n">
@@ -17628,7 +17628,7 @@
       </c>
       <c r="B1147" t="inlineStr">
         <is>
-          <t>User experience design 5</t>
+          <t>User experience design 2</t>
         </is>
       </c>
       <c r="C1147" t="n">
@@ -17643,7 +17643,7 @@
       </c>
       <c r="B1148" t="inlineStr">
         <is>
-          <t>User experience design 3</t>
+          <t>User experience design 4</t>
         </is>
       </c>
       <c r="C1148" t="n">
@@ -17673,7 +17673,7 @@
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>User experience design 4</t>
+          <t>User experience design 3</t>
         </is>
       </c>
       <c r="C1150" t="n">
@@ -17703,7 +17703,7 @@
       </c>
       <c r="B1152" t="inlineStr">
         <is>
-          <t>User experience design 3</t>
+          <t>User experience design 4</t>
         </is>
       </c>
       <c r="C1152" t="n">
@@ -17718,7 +17718,7 @@
       </c>
       <c r="B1153" t="inlineStr">
         <is>
-          <t>User experience analysis 3</t>
+          <t>User experience analysis 4</t>
         </is>
       </c>
       <c r="C1153" t="n">
@@ -17748,7 +17748,7 @@
       </c>
       <c r="B1155" t="inlineStr">
         <is>
-          <t>User experience analysis 4</t>
+          <t>User experience analysis 3</t>
         </is>
       </c>
       <c r="C1155" t="n">
@@ -17778,7 +17778,7 @@
       </c>
       <c r="B1157" t="inlineStr">
         <is>
-          <t>User experience analysis 3</t>
+          <t>User experience analysis 2</t>
         </is>
       </c>
       <c r="C1157" t="n">
@@ -17793,7 +17793,7 @@
       </c>
       <c r="B1158" t="inlineStr">
         <is>
-          <t>User experience analysis 2</t>
+          <t>User experience analysis 3</t>
         </is>
       </c>
       <c r="C1158" t="n">
@@ -17808,7 +17808,7 @@
       </c>
       <c r="B1159" t="inlineStr">
         <is>
-          <t>Animation development 4</t>
+          <t>Animation development 2</t>
         </is>
       </c>
       <c r="C1159" t="n">
@@ -17838,7 +17838,7 @@
       </c>
       <c r="B1161" t="inlineStr">
         <is>
-          <t>Animation development 2</t>
+          <t>Animation development 4</t>
         </is>
       </c>
       <c r="C1161" t="n">
@@ -17853,7 +17853,7 @@
       </c>
       <c r="B1162" t="inlineStr">
         <is>
-          <t>User experience design 4</t>
+          <t>User experience design 3</t>
         </is>
       </c>
       <c r="C1162" t="n">
@@ -17883,7 +17883,7 @@
       </c>
       <c r="B1164" t="inlineStr">
         <is>
-          <t>User experience design 3</t>
+          <t>User experience design 4</t>
         </is>
       </c>
       <c r="C1164" t="n">
